--- a/data/flight/titer/Scere_BC_LSMMG_1B.xlsx
+++ b/data/flight/titer/Scere_BC_LSMMG_1B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ipjos\code\DARPA\data\flight\growth\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ipjos\code\DARPA_FINAL\data\flight_uploaded_to_github_with_96_hours\growth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA86E460-0CAA-4CBA-B2BB-A79A1F8D2812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5169696-21C0-48D1-874D-171859CE6B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2820" yWindow="1050" windowWidth="24915" windowHeight="14850" xr2:uid="{CEFD99FE-FE29-BA4C-8E21-C28CFAD6EEDC}"/>
+    <workbookView xWindow="2415" yWindow="1950" windowWidth="26385" windowHeight="14250" activeTab="1" xr2:uid="{CEFD99FE-FE29-BA4C-8E21-C28CFAD6EEDC}"/>
   </bookViews>
   <sheets>
     <sheet name="1g growth" sheetId="1" r:id="rId1"/>
@@ -113,7 +113,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -152,6 +152,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -170,11 +181,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -197,10 +209,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{67D9F53B-9FF0-4776-B747-CE93A0C9B94D}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{B509A8C7-ED7F-4B22-AFB8-75BAF40290BD}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -581,31 +598,31 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
-        <v>59.783000000000001</v>
+        <v>96</v>
       </c>
-      <c r="B3" s="1">
-        <v>1.4967999999999999</v>
+      <c r="B3" s="8">
+        <v>1.4408000000000001</v>
       </c>
-      <c r="C3" s="1">
-        <v>1.3928</v>
+      <c r="C3" s="8">
+        <v>1.4448000000000001</v>
       </c>
-      <c r="D3" s="1">
-        <v>1.7847999999999999</v>
+      <c r="D3" s="8">
+        <v>1.5127999999999999</v>
       </c>
-      <c r="E3" s="1">
-        <v>1.4168000000000001</v>
+      <c r="E3" s="8">
+        <v>1.3968</v>
       </c>
-      <c r="F3" s="1">
-        <v>1.8168</v>
+      <c r="F3" s="8">
+        <v>1.5167999999999999</v>
       </c>
-      <c r="G3" s="1">
-        <v>1.5728</v>
+      <c r="G3" s="8">
+        <v>1.4328000000000001</v>
       </c>
-      <c r="H3" s="1">
-        <v>1.5608</v>
+      <c r="H3" s="8">
+        <v>1.4368000000000001</v>
       </c>
-      <c r="I3" s="1">
-        <v>1.5167999999999999</v>
+      <c r="I3" s="8">
+        <v>1.4288000000000001</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -633,9 +650,6 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -8757,40 +8771,43 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
-        <v>59.783000000000001</v>
+        <v>96</v>
       </c>
-      <c r="B3" s="1">
-        <v>0.16025641025641021</v>
+      <c r="B3" s="8">
+        <v>4.9432938856015776</v>
       </c>
-      <c r="C3" s="1">
-        <v>0.30818540433925057</v>
+      <c r="C3" s="8">
+        <v>4.9926035502958586</v>
       </c>
-      <c r="D3" s="1">
-        <v>0.45611439842209078</v>
+      <c r="D3" s="8">
+        <v>4.1296844181459562</v>
       </c>
-      <c r="E3" s="1">
-        <v>0.40680473372781067</v>
+      <c r="E3" s="8">
+        <v>3.9571005917159758</v>
       </c>
-      <c r="F3" s="1">
-        <v>0.67800788954635094</v>
+      <c r="F3" s="8">
+        <v>4.6474358974358969</v>
       </c>
-      <c r="G3">
-        <v>0.62869822485207094</v>
+      <c r="G3" s="9">
+        <v>4.696745562130177</v>
       </c>
-      <c r="H3">
-        <v>0.50542406311637089</v>
+      <c r="H3" s="9">
+        <v>4.6227810650887573</v>
       </c>
-      <c r="I3">
-        <v>0.43145956607495073</v>
+      <c r="I3" s="9">
+        <v>4.6474358974358969</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
